--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="681">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1573,7 +1573,7 @@
     <t>Patient.gender</t>
   </si>
   <si>
-    <t>Code issu du JDV_J143_AdministrativeGender_CISIS (1.2.250.1.213.1.1.5.590).</t>
+    <t>male | female | other | unknown</t>
   </si>
   <si>
     <t>French patient's gender checked with the INSi teleservice | Genre du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs sont M ou F</t>
@@ -1922,9 +1922,6 @@
   </si>
   <si>
     <t>Patient.contact.gender</t>
-  </si>
-  <si>
-    <t>male | female | other | unknown</t>
   </si>
   <si>
     <t>Administrative Gender - the gender that the contact person is considered to have for administration and record keeping purposes.</t>
@@ -17199,14 +17196,14 @@
         <v>168</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
@@ -17279,7 +17276,7 @@
         <v>80</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>80</v>
@@ -17287,10 +17284,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17316,14 +17313,14 @@
         <v>303</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -17372,7 +17369,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17381,13 +17378,13 @@
         <v>88</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>106</v>
@@ -17396,7 +17393,7 @@
         <v>80</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>80</v>
@@ -17404,10 +17401,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17433,10 +17430,10 @@
         <v>296</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17487,7 +17484,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17502,7 +17499,7 @@
         <v>100</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>106</v>
@@ -17519,10 +17516,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17548,16 +17545,16 @@
         <v>548</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>80</v>
@@ -17606,7 +17603,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17621,10 +17618,10 @@
         <v>100</v>
       </c>
       <c r="AK129" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AL129" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>80</v>
@@ -17638,10 +17635,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17753,10 +17750,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17870,10 +17867,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17989,10 +17986,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18018,16 +18015,16 @@
         <v>270</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>80</v>
@@ -18076,7 +18073,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>88</v>
@@ -18091,16 +18088,16 @@
         <v>100</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="AM133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>80</v>
@@ -18108,10 +18105,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18137,16 +18134,16 @@
         <v>379</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>80</v>
@@ -18195,7 +18192,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -18210,16 +18207,16 @@
         <v>100</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AL134" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AL134" t="s" s="2">
+      <c r="AM134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>80</v>
@@ -18227,14 +18224,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18253,16 +18250,16 @@
         <v>80</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18312,7 +18309,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18327,7 +18324,7 @@
         <v>100</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>106</v>
@@ -18336,7 +18333,7 @@
         <v>80</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>80</v>
@@ -18344,10 +18341,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18370,19 +18367,19 @@
         <v>89</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>80</v>
@@ -18431,7 +18428,7 @@
         <v>80</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18446,10 +18443,10 @@
         <v>100</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>80</v>
@@ -18463,10 +18460,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18492,16 +18489,16 @@
         <v>548</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>80</v>
@@ -18550,7 +18547,7 @@
         <v>80</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18565,7 +18562,7 @@
         <v>100</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>106</v>
@@ -18582,10 +18579,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18697,10 +18694,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18814,10 +18811,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18933,10 +18930,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18959,16 +18956,16 @@
         <v>89</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19018,7 +19015,7 @@
         <v>80</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>88</v>
@@ -19042,7 +19039,7 @@
         <v>80</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>80</v>
@@ -19050,10 +19047,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19079,10 +19076,10 @@
         <v>168</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19112,11 +19109,11 @@
         <v>264</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="Z142" t="s" s="2">
-        <v>680</v>
-      </c>
       <c r="AA142" t="s" s="2">
         <v>80</v>
       </c>
@@ -19133,7 +19130,7 @@
         <v>80</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>88</v>
@@ -19148,7 +19145,7 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>106</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
